--- a/outputs/daily/hr_rankings_2026-08-02.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-02.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -6114,7 +6114,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -7060,7 +7060,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -7360,7 +7360,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -7960,7 +7960,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -8560,7 +8560,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -8860,7 +8860,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -9460,7 +9460,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -10060,7 +10060,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -10660,7 +10660,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -10960,7 +10960,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -11260,7 +11260,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -11860,7 +11860,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-08-02.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-02.xlsx
@@ -780,7 +780,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4080,7 +4080,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6826,7 +6826,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -8626,7 +8626,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -10426,7 +10426,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -10726,7 +10726,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -11026,7 +11026,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -11326,7 +11326,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -11626,7 +11626,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
